--- a/surgical_staging/STAGED_CRS620MI_Supplier___Reference.xlsx
+++ b/surgical_staging/STAGED_CRS620MI_Supplier___Reference.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
   <si>
     <t>IRCONO</t>
   </si>
@@ -61,37 +61,40 @@
     <t>100.0</t>
   </si>
   <si>
-    <t xml:space="preserve">500970    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">501023    </t>
+    <t xml:space="preserve">502125    </t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
     <t xml:space="preserve">1         </t>
   </si>
   <si>
-    <t xml:space="preserve">2         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gayle Reed  glreed@soarus.com       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Krutsch bkrutsch@soarus.com   </t>
-  </si>
-  <si>
-    <t>nacs-customerservice@sunchemical.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">847-255-1211    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(224) 347-2312  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-866-786-8144  </t>
+    <t xml:space="preserve">Jeff Taylor                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">jeff.taylor@ingeniapolymers.com     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mindy Hoarston - Regional Sales MGR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">minday.hoarston@ingeniapolymers.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-519-758-8941  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">678-427-1863    </t>
   </si>
   <si>
     <t xml:space="preserve">                </t>
@@ -100,46 +103,37 @@
     <t xml:space="preserve">                    </t>
   </si>
   <si>
-    <t>SR. CUSTOMER SERVICE COORDINAT</t>
-  </si>
-  <si>
-    <t>TECHNICAL SALES REPRESENTATIVE</t>
+    <t xml:space="preserve">EXT 1002                      </t>
   </si>
   <si>
     <t xml:space="preserve">                              </t>
   </si>
   <si>
-    <t>20020805.0</t>
-  </si>
-  <si>
-    <t>20180419.0</t>
-  </si>
-  <si>
-    <t>20180914.0</t>
-  </si>
-  <si>
-    <t>140113.0</t>
-  </si>
-  <si>
-    <t>140315.0</t>
-  </si>
-  <si>
-    <t>104629.0</t>
-  </si>
-  <si>
-    <t>20180912.0</t>
+    <t>20180904.0</t>
+  </si>
+  <si>
+    <t>125427.0</t>
+  </si>
+  <si>
+    <t>125436.0</t>
+  </si>
+  <si>
+    <t>125501.0</t>
+  </si>
+  <si>
+    <t>125556.0</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2.0</t>
   </si>
   <si>
     <t>3.0</t>
   </si>
   <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W20PUDAB  </t>
+    <t>4.0</t>
   </si>
   <si>
     <t xml:space="preserve">W20PUCAJ  </t>
@@ -500,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -555,40 +549,40 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
         <v>31</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -602,37 +596,37 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
         <v>29</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
         <v>37</v>
       </c>
-      <c r="M3" t="s">
-        <v>39</v>
-      </c>
       <c r="N3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -640,43 +634,87 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
         <v>30</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" t="s">
         <v>40</v>
       </c>
-      <c r="N4" t="s">
-        <v>42</v>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/surgical_staging/STAGED_CRS620MI_Supplier___Reference.xlsx
+++ b/surgical_staging/STAGED_CRS620MI_Supplier___Reference.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="119">
   <si>
     <t>IRCONO</t>
   </si>
@@ -61,6 +61,21 @@
     <t>100.0</t>
   </si>
   <si>
+    <t xml:space="preserve">500003    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">376047    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">136036    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">140376    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">379811    </t>
+  </si>
+  <si>
     <t xml:space="preserve">502125    </t>
   </si>
   <si>
@@ -73,12 +88,72 @@
     <t>30</t>
   </si>
   <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>35</t>
   </si>
   <si>
     <t xml:space="preserve">1         </t>
   </si>
   <si>
+    <t xml:space="preserve">2         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REP       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTACT   </t>
+  </si>
+  <si>
+    <t>SECURITY #</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAX ID #  </t>
+  </si>
+  <si>
+    <t>ACCOUNTING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSR       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAX ID#   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yolanda Castellano                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Gloriso                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kathy McGRAW                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sabrina Gandy                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gayle Reed                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVI# dowImp01400                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">36-4079419                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nate Poulos                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sabrina GANDY                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letter rec'd May 7, 2009 see below  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAX ID# 38-1285128                  </t>
+  </si>
+  <si>
     <t xml:space="preserve">Jeff Taylor                         </t>
   </si>
   <si>
@@ -91,27 +166,150 @@
     <t xml:space="preserve">minday.hoarston@ingeniapolymers.com </t>
   </si>
   <si>
+    <t xml:space="preserve">(888) 333-7607  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">914-260-7508    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(989) 832-1087  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(847) 255-1211  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(989) 832-1399  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">989-832-1087    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">847-253-1285    </t>
+  </si>
+  <si>
     <t xml:space="preserve">1-519-758-8941  </t>
   </si>
   <si>
     <t xml:space="preserve">678-427-1863    </t>
   </si>
   <si>
-    <t xml:space="preserve">                </t>
+    <t xml:space="preserve">(914) 631-7278  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">727-239-7556    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXT: 10         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">866-922-8435    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">847-255-4343    </t>
   </si>
   <si>
     <t xml:space="preserve">                    </t>
   </si>
   <si>
+    <t xml:space="preserve">CUSTOMER SERVICE              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCT EXEC                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGANDY@DOW.COM                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREED@SOARUS.COM              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPOULOS@DOW.COM               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WWW.EHCMA.COM/SECURITY        </t>
+  </si>
+  <si>
     <t xml:space="preserve">EXT 1002                      </t>
   </si>
   <si>
-    <t xml:space="preserve">                              </t>
+    <t>20000912.0</t>
+  </si>
+  <si>
+    <t>20011217.0</t>
+  </si>
+  <si>
+    <t>20040113.0</t>
+  </si>
+  <si>
+    <t>20040114.0</t>
+  </si>
+  <si>
+    <t>20090505.0</t>
+  </si>
+  <si>
+    <t>20050113.0</t>
+  </si>
+  <si>
+    <t>20060928.0</t>
+  </si>
+  <si>
+    <t>20070402.0</t>
+  </si>
+  <si>
+    <t>20090507.0</t>
+  </si>
+  <si>
+    <t>20131009.0</t>
+  </si>
+  <si>
+    <t>20170404.0</t>
   </si>
   <si>
     <t>20180904.0</t>
   </si>
   <si>
+    <t>95846.0</t>
+  </si>
+  <si>
+    <t>95920.0</t>
+  </si>
+  <si>
+    <t>103157.0</t>
+  </si>
+  <si>
+    <t>172456.0</t>
+  </si>
+  <si>
+    <t>85555.0</t>
+  </si>
+  <si>
+    <t>170128.0</t>
+  </si>
+  <si>
+    <t>160304.0</t>
+  </si>
+  <si>
+    <t>134538.0</t>
+  </si>
+  <si>
+    <t>152120.0</t>
+  </si>
+  <si>
+    <t>124130.0</t>
+  </si>
+  <si>
+    <t>163531.0</t>
+  </si>
+  <si>
+    <t>115807.0</t>
+  </si>
+  <si>
     <t>125427.0</t>
   </si>
   <si>
@@ -124,19 +322,55 @@
     <t>125556.0</t>
   </si>
   <si>
+    <t>20101019.0</t>
+  </si>
+  <si>
+    <t>20120727.0</t>
+  </si>
+  <si>
+    <t>20131119.0</t>
+  </si>
+  <si>
+    <t>20061012.0</t>
+  </si>
+  <si>
+    <t>20140611.0</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
     <t>1.0</t>
   </si>
   <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>3.0</t>
-  </si>
-  <si>
     <t>4.0</t>
   </si>
   <si>
+    <t xml:space="preserve">W20PUNEW  </t>
+  </si>
+  <si>
     <t xml:space="preserve">W20PUCAJ  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W25ACMEM  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W15PUDAH  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W15PUSYC  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W25MKSEM  </t>
   </si>
 </sst>
 </file>
@@ -494,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -549,40 +783,40 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="N2" t="s">
-        <v>40</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -593,40 +827,40 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="M3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="N3" t="s">
-        <v>40</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -634,43 +868,43 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="L4" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="M4" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="N4" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -678,43 +912,571 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" t="s">
+        <v>104</v>
+      </c>
+      <c r="M5" t="s">
+        <v>107</v>
+      </c>
+      <c r="N5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" t="s">
+        <v>90</v>
+      </c>
+      <c r="L6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M6" t="s">
+        <v>110</v>
+      </c>
+      <c r="N6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L7" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" t="s">
+        <v>111</v>
+      </c>
+      <c r="N7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" t="s">
+        <v>92</v>
+      </c>
+      <c r="L8" t="s">
+        <v>79</v>
+      </c>
+      <c r="M8" t="s">
+        <v>111</v>
+      </c>
+      <c r="N8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" t="s">
+        <v>106</v>
+      </c>
+      <c r="M9" t="s">
+        <v>110</v>
+      </c>
+      <c r="N9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" t="s">
+        <v>103</v>
+      </c>
+      <c r="M10" t="s">
+        <v>107</v>
+      </c>
+      <c r="N10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" t="s">
+        <v>82</v>
+      </c>
+      <c r="M11" t="s">
+        <v>111</v>
+      </c>
+      <c r="N11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" t="s">
+        <v>83</v>
+      </c>
+      <c r="M12" t="s">
+        <v>111</v>
+      </c>
+      <c r="N12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" t="s">
+        <v>84</v>
+      </c>
+      <c r="M13" t="s">
+        <v>111</v>
+      </c>
+      <c r="N13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" t="s">
         <v>26</v>
       </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" t="s">
-        <v>40</v>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" t="s">
+        <v>85</v>
+      </c>
+      <c r="M14" t="s">
+        <v>111</v>
+      </c>
+      <c r="N14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" t="s">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L15" t="s">
+        <v>85</v>
+      </c>
+      <c r="M15" t="s">
+        <v>110</v>
+      </c>
+      <c r="N15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J16" t="s">
+        <v>85</v>
+      </c>
+      <c r="K16" t="s">
+        <v>100</v>
+      </c>
+      <c r="L16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M16" t="s">
+        <v>108</v>
+      </c>
+      <c r="N16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" t="s">
+        <v>68</v>
+      </c>
+      <c r="J17" t="s">
+        <v>85</v>
+      </c>
+      <c r="K17" t="s">
+        <v>101</v>
+      </c>
+      <c r="L17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M17" t="s">
+        <v>112</v>
+      </c>
+      <c r="N17" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
